--- a/src/test/java/tests/K19_ExcelOtomasyon/ulkeler.xlsx
+++ b/src/test/java/tests/K19_ExcelOtomasyon/ulkeler.xlsx
@@ -12,6 +12,8 @@
     <sheet name="Sayfa2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet1" sheetId="3" r:id="rId3"/>
     <sheet name="Sheet2" sheetId="4" r:id="rId4"/>
+    <sheet name="Sayfa3" r:id="rId8" sheetId="5"/>
+    <sheet name="FenerbahceKadro" r:id="rId9" sheetId="6"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -23,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="773" uniqueCount="577">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="787" uniqueCount="581">
   <si>
     <t>Ülke (İngilizce)</t>
   </si>
@@ -1754,6 +1756,18 @@
   </si>
   <si>
     <t>Selenium</t>
+  </si>
+  <si>
+    <t>Fenerbahçe</t>
+  </si>
+  <si>
+    <t>Kadıköy</t>
+  </si>
+  <si>
+    <t>Oppong</t>
+  </si>
+  <si>
+    <t>Gendouzi</t>
   </si>
 </sst>
 </file>
@@ -2181,7 +2195,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E193"/>
+  <dimension ref="A1:E195"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="4" customWidth="true" width="25.6640625" collapsed="true"/>
@@ -4886,6 +4900,22 @@
         <v>575</v>
       </c>
       <c r="B193" t="s" s="0">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="s" s="0">
+        <v>575</v>
+      </c>
+      <c r="B194" t="s" s="0">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="s" s="0">
+        <v>575</v>
+      </c>
+      <c r="B195" t="s" s="0">
         <v>576</v>
       </c>
     </row>
@@ -4985,4 +5015,43 @@
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="0">
+        <v>577</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>578</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>579</v>
+      </c>
+      <c r="C1" t="s" s="0">
+        <v>580</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>